--- a/papers/P002/P002_工程复现问题清单_v1.xlsx
+++ b/papers/P002/P002_工程复现问题清单_v1.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Aptos"/>
@@ -19,12 +19,6 @@
       <sz val="11"/>
       <name val="Aptos"/>
       <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos"/>
-      <u/>
-      <color rgb="FF0563C1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -59,18 +53,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -82,14 +73,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="25"/>
+  <sheetFormatPr defaultRowHeight="24"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="95" customWidth="1"/>
+    <col min="2" max="2" width="51" customWidth="1"/>
+    <col min="3" max="3" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">主题</t>
@@ -106,7 +97,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="155" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">金融专题Agent</t>
@@ -114,16 +105,16 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">七层21类金融Agent分别有哪些？如何实现？</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">I市场周期/波动状态(2)；II尾部风险/崩盘预警(2)；III流动性/订单失衡/量价协同/成交量结构(4)；IV趋势/反转/区间波动/滞后响应/波动非对称(5)；V回撤/分形(2)；VI状态门控/稳定性(2)；VII K线形态/创造性设计/因子组合/羊群效应(4)。每类有专门金融任务Prompt，不是21个微调模型。详见作者21个原始Prompt：https://github.com/uwFengyuan/CogAlpha_Prompt/tree/main/prompts/seven_level_agent_hierarchy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="93" customHeight="1">
+          <t xml:space="preserve">21个金融专题Agent怎样分工，具体靠什么实现？</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">作者按7个金融研究层级定义21种专业角色。每种角色以独立的研究任务Intro和因子设计Guidance，搭配统一的代码与输出模板组成Prompt；并不是21个分别微调的模型。具体分类及每份原始Prompt，点击查看：https://github.com/epshoron/JXwork/blob/main/papers/P002/P002_AGENT_TOPICS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="86" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">模型与Agent实现</t>
@@ -140,7 +131,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="93" customHeight="1">
+    <row r="4" ht="86" customHeight="1">
       <c r="A4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">五种Guidance</t>
@@ -157,7 +148,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="93" customHeight="1">
+    <row r="5" ht="86" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">代码输入输出</t>
@@ -174,7 +165,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="93" customHeight="1">
+    <row r="6" ht="86" customHeight="1">
       <c r="A6" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">质量检查</t>
@@ -191,7 +182,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="93" customHeight="1">
+    <row r="7" ht="86" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">预测评分</t>
@@ -208,7 +199,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="93" customHeight="1">
+    <row r="8" ht="86" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">保留规则</t>
@@ -225,7 +216,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="93" customHeight="1">
+    <row r="9" ht="86" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">反馈再生成</t>
@@ -242,7 +233,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="93" customHeight="1">
+    <row r="10" ht="86" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">显式与隐式遗传</t>
@@ -259,7 +250,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="93" customHeight="1">
+    <row r="11" ht="86" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Mutation与Crossover</t>
@@ -276,7 +267,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="93" customHeight="1">
+    <row r="12" ht="86" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">两路衔接</t>
@@ -293,7 +284,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="93" customHeight="1">
+    <row r="13" ht="86" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">循环控制</t>
@@ -310,7 +301,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="93" customHeight="1">
+    <row r="14" ht="86" customHeight="1">
       <c r="A14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">公开实现与复现</t>
@@ -330,7 +321,7 @@
   </sheetData>
   <autoFilter ref="A1:C14"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="点击打开作者21个Agent Prompt目录"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="点击阅读七层21个专题及原始Prompt"/>
   </hyperlinks>
 </worksheet>
 </file>
--- a/papers/P002/P002_工程复现问题清单_v1.xlsx
+++ b/papers/P002/P002_工程复现问题清单_v1.xlsx
@@ -36,7 +36,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F5FA"/>
+        <fgColor rgb="FFF1F5F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -72,15 +72,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="24"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="92" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="3" max="3" width="103" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">主题</t>
@@ -97,7 +97,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="100" customHeight="1">
+    <row r="2" ht="103" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">金融专题Agent</t>
@@ -114,7 +114,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="86" customHeight="1">
+    <row r="3" ht="93" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">模型与Agent实现</t>
@@ -131,7 +131,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="86" customHeight="1">
+    <row r="4" ht="103" customHeight="1">
       <c r="A4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">五种Guidance</t>
@@ -148,180 +148,214 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="86" customHeight="1">
+    <row r="5" ht="93" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">初始输入与Prompt装配</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">专题Agent从哪些输入开始？是单独的结构化市场状态还是Prompt？</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">从OHLCV字段说明、预测区间和金融专题指引开始；作者公开模板将System、角色Intro、可选成败样例、通用要求、专题Guidance和代码输出格式拼成聊天Prompt，Guidance还可先改写。没有在该组模板中看到P005式每日市场摘要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="93" customHeight="1">
+      <c r="A6" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">代码输入输出</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="2">
+      <c r="B6" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">初始生成的Python因子长什么样？</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr" s="2">
+      <c r="C6" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">专题Agent根据OHLCV和Prompt输出可执行Python函数factor_...(df)，返回对齐(date,ticker)的pd.Series；不是先搜索固定运算符语法树。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="86" customHeight="1">
-      <c r="A6" t="inlineStr" s="0">
+    <row r="7" ht="93" customHeight="1">
+      <c r="A7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">质量检查</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="0">
+      <c r="B7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Quality Checker由谁组成，具体检查什么？</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="0">
+      <c r="C7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Code Quality查语法/运行问题→Code Repair修复；Judge审金融逻辑→Logic Improvement修正；通过后检查数值稳定、NaN、越界和未来信息泄漏，无法修复者淘汰。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="86" customHeight="1">
-      <c r="A7" t="inlineStr" s="2">
+    <row r="8" ht="93" customHeight="1">
+      <c r="A8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">预测评分</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr" s="2">
+      <c r="B8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">预测能力到底按哪些指标打分？</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr" s="2">
+      <c r="C8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">IC、RankIC检验与未来收益的线性/排序相关；ICIR、RankICIR检验这些相关性在时间上的稳定性；MI衡量非线性依赖。五指标是实际数据计算的Fitness，不是让LLM主观给分。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="86" customHeight="1">
-      <c r="A8" t="inlineStr" s="0">
+    <row r="9" ht="93" customHeight="1">
+      <c r="A9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">保留规则</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr" s="0">
+      <c r="B9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">哪些因子可以成为父代和精英？</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr" s="0">
+      <c r="C9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">五项Fitness需同时超过同代第65百分位和相应绝对下限才合格；精英门槛为第80百分位及更高绝对下限。合格者进父代池，前代最好的2个精英保留。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="86" customHeight="1">
-      <c r="A9" t="inlineStr" s="2">
+    <row r="10" ht="93" customHeight="1">
+      <c r="A10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">单因子评分还是整池边际</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">入选父代池时，会像P005那样计算新增因子给整个组合池带来的增益吗？</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">不是。候选按自身IC、RankIC、ICIR、RankICIR、MI及分位数/绝对门槛进入父代池或精英池；此筛选不是计算Γ(P∪{f})−Γ(P)。用于进化的父代种群不同于P005为预测而维护的加权因子组合池。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="83" customHeight="1">
+      <c r="A11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">反馈再生成</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="2">
+      <c r="B11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">成功/失败经验怎样改变下一轮生成？</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr" s="2">
+      <c r="C11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">每代选2个有效因子和2个最差无效因子，提炼原因连同表现写入下一轮生成Prompt。更新的是提示上下文，不是模型参数。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="86" customHeight="1">
-      <c r="A10" t="inlineStr" s="0">
+    <row r="12" ht="93" customHeight="1">
+      <c r="A12" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">显式与隐式遗传</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="0">
+      <c r="B12" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">老师问显性还是隐性，准确应怎样回答？</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="0">
+      <c r="C12" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">“显式/隐式”是工程实现维度，不是遗传算法正式的二选一名称。显式的是外部程序管理种群、评分、筛选、父代和精英；隐式的是LLM依Prompt理解父代代码并生成变化，不是预先编程好的AST节点交换。CogAlpha两者结合。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="86" customHeight="1">
-      <c r="A11" t="inlineStr" s="2">
+    <row r="13" ht="103" customHeight="1">
+      <c r="A13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Mutation与Crossover</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr" s="2">
+      <c r="B13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">变异和交叉具体通过什么实现？</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr" s="2">
+      <c r="C13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Mutation把1份父代Python填到{original_factor_code}，LLM调整窗口/变换/归一化等；Crossover把2份父代填到{parent_factor_1_code}和{parent_factor_2_code}，LLM融合金融逻辑生成新函数。三条路径：仅变异、仅交叉、先交叉再变异。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="86" customHeight="1">
-      <c r="A12" t="inlineStr" s="0">
+    <row r="14" ht="93" customHeight="1">
+      <c r="A14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">两路衔接</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr" s="0">
+      <c r="B14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">最初Python生成和遗传搜索是怎样连接、是否持续并行？</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr" s="0">
+      <c r="C14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">21个专题中随机选13个，每个约生5–6个候选，初始约80个→质检/评分→最多32个父代→各代进化生成至少96个子代；每隔2代还向父代池注入专题Agent新生成且通过过滤的因子。它们周期性汇流，但论文不证明计算上是两个并发进程。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="86" customHeight="1">
-      <c r="A13" t="inlineStr" s="2">
+    <row r="15" ht="83" customHeight="1">
+      <c r="A15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">循环控制</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="2">
+      <c r="B15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">进化持续多少代，何时停止？</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr" s="2">
+      <c r="C15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">默认24代，3个子周期、每个8代；子代继续质检和评分，最佳2个精英继承；此外有精英表现平台期改进≤0.001的提前停止判据。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="86" customHeight="1">
-      <c r="A14" t="inlineStr" s="0">
+    <row r="16" ht="93" customHeight="1">
+      <c r="A16" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">公开实现与复现</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr" s="0">
+      <c r="B16" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">是否有完整工程代码、能够直接运行？</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr" s="0">
+      <c r="C16" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">公开的是金融角色、Guidance、质检和Mutation/Crossover等Prompt；没有完整的演化调度/评价/执行仓库，因此已核实Prompt写法和论文方法，但未复现完整工程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
+  <autoFilter ref="A1:C16"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="点击阅读七层21个专题及原始Prompt"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="打开原始资料链接"/>
   </hyperlinks>
 </worksheet>
 </file>
--- a/papers/P002/P002_工程复现问题清单_v1.xlsx
+++ b/papers/P002/P002_工程复现问题清单_v1.xlsx
@@ -36,7 +36,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
+        <fgColor rgb="FFF2F5F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -55,13 +55,13 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -72,15 +72,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="103" customWidth="1"/>
+    <col min="2" max="2" width="53" customWidth="1"/>
+    <col min="3" max="3" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">主题</t>
@@ -97,7 +97,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="103" customHeight="1">
+    <row r="2" ht="122" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">金融专题Agent</t>
@@ -114,7 +114,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="93" customHeight="1">
+    <row r="3" ht="94" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">模型与Agent实现</t>
@@ -131,7 +131,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="103" customHeight="1">
+    <row r="4" ht="108" customHeight="1">
       <c r="A4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">五种Guidance</t>
@@ -148,7 +148,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="93" customHeight="1">
+    <row r="5" ht="94" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">初始输入与Prompt装配</t>
@@ -165,7 +165,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="93" customHeight="1">
+    <row r="6" ht="94" customHeight="1">
       <c r="A6" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">代码输入输出</t>
@@ -182,7 +182,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="93" customHeight="1">
+    <row r="7" ht="94" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">质量检查</t>
@@ -199,7 +199,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="93" customHeight="1">
+    <row r="8" ht="94" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">预测评分</t>
@@ -216,7 +216,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="93" customHeight="1">
+    <row r="9" ht="82" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">保留规则</t>
@@ -233,7 +233,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="93" customHeight="1">
+    <row r="10" ht="94" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">单因子评分还是整池边际</t>
@@ -250,7 +250,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="83" customHeight="1">
+    <row r="11" ht="82" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">反馈再生成</t>
@@ -267,7 +267,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="93" customHeight="1">
+    <row r="12" ht="94" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">显式与隐式遗传</t>
@@ -284,7 +284,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="103" customHeight="1">
+    <row r="13" ht="108" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Mutation与Crossover</t>
@@ -301,7 +301,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="93" customHeight="1">
+    <row r="14" ht="94" customHeight="1">
       <c r="A14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">两路衔接</t>
@@ -318,44 +318,61 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="83" customHeight="1">
+    <row r="15" ht="94" customHeight="1">
       <c r="A15" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">搜索调度与优化对象</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">谁决定下一代做什么？是否有Bandit在因子和预测模型之间切换？</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">没有P006式Factor/Model双臂调度。P002按预设种群进化流程选父代、调用LLM作变异/交叉，并周期性注入专题Agent新因子；它优化因子候选，后续LightGBM/Ridge等预测器是评价/下游模块，未在同一搜索中由LLM交替提出模型架构。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="82" customHeight="1">
+      <c r="A16" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">循环控制</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr" s="2">
+      <c r="B16" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">进化持续多少代，何时停止？</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr" s="2">
+      <c r="C16" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">默认24代，3个子周期、每个8代；子代继续质检和评分，最佳2个精英继承；此外有精英表现平台期改进≤0.001的提前停止判据。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="93" customHeight="1">
-      <c r="A16" t="inlineStr" s="0">
+    <row r="17" ht="94" customHeight="1">
+      <c r="A17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">公开实现与复现</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr" s="0">
+      <c r="B17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">是否有完整工程代码、能够直接运行？</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr" s="0">
+      <c r="C17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">公开的是金融角色、Guidance、质检和Mutation/Crossover等Prompt；没有完整的演化调度/评价/执行仓库，因此已核实Prompt写法和论文方法，但未复现完整工程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C16"/>
+  <autoFilter ref="A1:C17"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="打开原始资料链接"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="打开相关公开资料"/>
   </hyperlinks>
 </worksheet>
 </file>
--- a/papers/P002/P002_工程复现问题清单_v1.xlsx
+++ b/papers/P002/P002_工程复现问题清单_v1.xlsx
@@ -30,7 +30,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF142B46"/>
+        <fgColor rgb="FF172D48"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -72,12 +72,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="53" customWidth="1"/>
-    <col min="3" max="3" width="92" customWidth="1"/>
+    <col min="3" max="3" width="98" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -97,282 +97,231 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="122" customHeight="1">
+    <row r="2" ht="96" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">金融专题Agent</t>
+          <t xml:space="preserve">金融Agent与LLM底座</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">21个金融专题Agent怎样分工，具体靠什么实现？</t>
+          <t xml:space="preserve">为什么有21个Agent？是21个独立微调模型吗？</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">作者按7个金融研究层级定义21种专业角色。每种角色以独立的研究任务Intro和因子设计Guidance，搭配统一的代码与输出模板组成Prompt；并不是21个分别微调的模型。具体分类及每份原始Prompt，点击查看：https://github.com/epshoron/JXwork/blob/main/papers/P002/P002_AGENT_TOPICS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="94" customHeight="1">
+          <t xml:space="preserve">21个金融专题角色覆盖7个层级，用不同Intro/Guidance Prompt调用默认gpt-oss-120b，而非21套微调权重。角色详情与原始Prompt：https://github.com/epshoron/JXwork/blob/main/papers/P002/P002_AGENT_TOPICS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="86" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模型与Agent实现</t>
+          <t xml:space="preserve">五种Guidance</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">底座是什么？靠微调还是Prompt限制？</t>
+          <t xml:space="preserve">所谓“五个限制词”到底是什么、如何输入？</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">论文所有Agent默认使用gpt-oss-120b；角色靠金融专题Prompt分工，未报告为21个角色分别微调或在进化中更新LLM权重；生成/演化Agent温度从0.7至1.2选取。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="108" customHeight="1">
+          <t xml:space="preserve">这是5种Guidance改写风格，不是5条硬性限制：light轻改、moderate适度、creative创意、divergent换视角、concrete给公式例子。程序把{guidance}和{rewrite_style}填进改写Prompt。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="86" customHeight="1">
       <c r="A4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">五种Guidance</t>
+          <t xml:space="preserve">初始输入与Prompt装配</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">所谓“五个限制词”到底是什么、如何输入？</t>
+          <t xml:space="preserve">专题Agent从哪些输入开始？是单独的结构化市场状态还是Prompt？</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">其实是研究指导的5种改写风格：light轻改写、moderate适度改写、creative创意深化、divergent切换相关视角、concrete给出可计算的比率/公式例子。由改写Prompt接收{guidance}和{rewrite_style}，输出不同版本指导语，不是5条硬限制。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="94" customHeight="1">
+          <t xml:space="preserve">从OHLCV字段说明、预测区间和金融专题指引开始；作者公开模板将System、角色Intro、可选成败样例、通用要求、专题Guidance和代码输出格式拼成聊天Prompt，Guidance还可先改写。没有在该组模板中看到P005式每日市场摘要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">初始输入与Prompt装配</t>
+          <t xml:space="preserve">代码输入输出</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">专题Agent从哪些输入开始？是单独的结构化市场状态还是Prompt？</t>
+          <t xml:space="preserve">初始生成的Python因子长什么样？</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">从OHLCV字段说明、预测区间和金融专题指引开始；作者公开模板将System、角色Intro、可选成败样例、通用要求、专题Guidance和代码输出格式拼成聊天Prompt，Guidance还可先改写。没有在该组模板中看到P005式每日市场摘要。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="94" customHeight="1">
+          <t xml:space="preserve">专题Agent根据OHLCV和Prompt输出可执行Python函数factor_...(df)，返回对齐(date,ticker)的pd.Series；不是先搜索固定运算符语法树。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="86" customHeight="1">
       <c r="A6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">代码输入输出</t>
+          <t xml:space="preserve">质量检查</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">初始生成的Python因子长什么样？</t>
+          <t xml:space="preserve">Quality Checker由谁组成，具体检查什么？</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">专题Agent根据OHLCV和Prompt输出可执行Python函数factor_...(df)，返回对齐(date,ticker)的pd.Series；不是先搜索固定运算符语法树。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="94" customHeight="1">
+          <t xml:space="preserve">Code Quality查语法/运行问题→Code Repair修复；Judge审金融逻辑→Logic Improvement修正；通过后检查数值稳定、NaN、越界和未来信息泄漏，无法修复者淘汰。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="86" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量检查</t>
+          <t xml:space="preserve">预测评分</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Quality Checker由谁组成，具体检查什么？</t>
+          <t xml:space="preserve">预测能力到底按哪些指标打分？</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Code Quality查语法/运行问题→Code Repair修复；Judge审金融逻辑→Logic Improvement修正；通过后检查数值稳定、NaN、越界和未来信息泄漏，无法修复者淘汰。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="94" customHeight="1">
+          <t xml:space="preserve">IC、RankIC检验与未来收益的线性/排序相关；ICIR、RankICIR检验这些相关性在时间上的稳定性；MI衡量非线性依赖。五指标是实际数据计算的Fitness，不是让LLM主观给分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">预测评分</t>
+          <t xml:space="preserve">父代筛选与精英保留</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">预测能力到底按哪些指标打分？</t>
+          <t xml:space="preserve">按单因子表现还是整池边际选父代？</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IC、RankIC检验与未来收益的线性/排序相关；ICIR、RankICIR检验这些相关性在时间上的稳定性；MI衡量非线性依赖。五指标是实际数据计算的Fitness，不是让LLM主观给分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="82" customHeight="1">
+          <t xml:space="preserve">每个因子五项Fitness需同时超过同代65%分位与绝对下限才进父代池；80%分位对应精英标准，并保留最佳2条。是单因子门槛筛选，不计算P005式组合池ΔΓ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保留规则</t>
+          <t xml:space="preserve">反馈再生成</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">哪些因子可以成为父代和精英？</t>
+          <t xml:space="preserve">成功/失败经验怎样改变下一轮生成？</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">五项Fitness需同时超过同代第65百分位和相应绝对下限才合格；精英门槛为第80百分位及更高绝对下限。合格者进父代池，前代最好的2个精英保留。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="94" customHeight="1">
+          <t xml:space="preserve">每代把2个有效和2个最差因子的代码、表现与失败原因放进下一轮Prompt；更新案例与生成上下文，不训练LLM权重。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">单因子评分还是整池边际</t>
+          <t xml:space="preserve">显式与隐式遗传</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">入选父代池时，会像P005那样计算新增因子给整个组合池带来的增益吗？</t>
+          <t xml:space="preserve">老师问显性还是隐性，准确应怎样回答？</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">不是。候选按自身IC、RankIC、ICIR、RankICIR、MI及分位数/绝对门槛进入父代池或精英池；此筛选不是计算Γ(P∪{f})−Γ(P)。用于进化的父代种群不同于P005为预测而维护的加权因子组合池。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="82" customHeight="1">
+          <t xml:space="preserve">两者并存：程序**显式**管理种群、评分、父代和精英；LLM依据父代代码与Prompt**隐式**生成变异/交叉结果，不是固定AST节点交换。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">反馈再生成</t>
+          <t xml:space="preserve">Mutation与Crossover</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">成功/失败经验怎样改变下一轮生成？</t>
+          <t xml:space="preserve">变异和交叉具体通过什么实现？</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">每代选2个有效因子和2个最差无效因子，提炼原因连同表现写入下一轮生成Prompt。更新的是提示上下文，不是模型参数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="94" customHeight="1">
+          <t xml:space="preserve">Mutation把1份父代Python填到{original_factor_code}，LLM调整窗口/变换/归一化等；Crossover把2份父代填到{parent_factor_1_code}和{parent_factor_2_code}，LLM融合金融逻辑生成新函数。三条路径：仅变异、仅交叉、先交叉再变异。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="78" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">显式与隐式遗传</t>
+          <t xml:space="preserve">两路衔接与调度</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">老师问显性还是隐性，准确应怎样回答？</t>
+          <t xml:space="preserve">初始专题生成与遗传进化如何衔接？会在因子/模型间切换吗？</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">“显式/隐式”是工程实现维度，不是遗传算法正式的二选一名称。显式的是外部程序管理种群、评分、筛选、父代和精英；隐式的是LLM依Prompt理解父代代码并生成变化，不是预先编程好的AST节点交换。CogAlpha两者结合。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="108" customHeight="1">
+          <t xml:space="preserve">初始随机选13个专题、生成约80条，经检查最多留32个父代；进化每代生成至少96个子代，每隔2代再注入专题Agent新因子。由程序调度因子进化，不用P006式Bandit改预测模型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="78" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Mutation与Crossover</t>
+          <t xml:space="preserve">循环控制</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">变异和交叉具体通过什么实现？</t>
+          <t xml:space="preserve">进化持续多少代，何时停止？</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Mutation把1份父代Python填到{original_factor_code}，LLM调整窗口/变换/归一化等；Crossover把2份父代填到{parent_factor_1_code}和{parent_factor_2_code}，LLM融合金融逻辑生成新函数。三条路径：仅变异、仅交叉、先交叉再变异。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="94" customHeight="1">
+          <t xml:space="preserve">默认24代（3段×8代）；每代仍做质检、评价和精英保留。另设精英改善≤0.001的平台期提前停止规则。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="86" customHeight="1">
       <c r="A14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">两路衔接</t>
+          <t xml:space="preserve">公开实现与复现</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">最初Python生成和遗传搜索是怎样连接、是否持续并行？</t>
+          <t xml:space="preserve">是否有完整工程代码、能够直接运行？</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">21个专题中随机选13个，每个约生5–6个候选，初始约80个→质检/评分→最多32个父代→各代进化生成至少96个子代；每隔2代还向父代池注入专题Agent新生成且通过过滤的因子。它们周期性汇流，但论文不证明计算上是两个并发进程。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="94" customHeight="1">
-      <c r="A15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">搜索调度与优化对象</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">谁决定下一代做什么？是否有Bandit在因子和预测模型之间切换？</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">没有P006式Factor/Model双臂调度。P002按预设种群进化流程选父代、调用LLM作变异/交叉，并周期性注入专题Agent新因子；它优化因子候选，后续LightGBM/Ridge等预测器是评价/下游模块，未在同一搜索中由LLM交替提出模型架构。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="82" customHeight="1">
-      <c r="A16" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">循环控制</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">进化持续多少代，何时停止？</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">默认24代，3个子周期、每个8代；子代继续质检和评分，最佳2个精英继承；此外有精英表现平台期改进≤0.001的提前停止判据。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="94" customHeight="1">
-      <c r="A17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">公开实现与复现</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">是否有完整工程代码、能够直接运行？</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr" s="2">
-        <is>
           <t xml:space="preserve">公开的是金融角色、Guidance、质检和Mutation/Crossover等Prompt；没有完整的演化调度/评价/执行仓库，因此已核实Prompt写法和论文方法，但未复现完整工程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C17"/>
+  <autoFilter ref="A1:C14"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="打开相关公开资料"/>
+    <hyperlink ref="C2" r:id="rId1" tooltip="打开相关来源或机制图解"/>
   </hyperlinks>
 </worksheet>
 </file>